--- a/data/trans_dic/P74B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 16,1</t>
+          <t>4,61; 15,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,23; 39,74</t>
+          <t>17,62; 38,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,97; 26,11</t>
+          <t>10,18; 26,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80,97; 97,62</t>
+          <t>78,21; 97,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,09; 80,9</t>
+          <t>56,65; 80,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,9; 60,31</t>
+          <t>35,66; 61,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,47; 38,93</t>
+          <t>23,98; 39,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,12; 53,93</t>
+          <t>37,04; 54,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,96; 37,23</t>
+          <t>23,0; 37,23</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 9,0</t>
+          <t>2,69; 9,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,05</t>
+          <t>5,13; 13,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,78</t>
+          <t>3,43; 9,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68,24; 84,94</t>
+          <t>68,68; 86,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,4; 76,11</t>
+          <t>60,3; 75,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,41; 71,29</t>
+          <t>56,16; 71,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,86; 30,52</t>
+          <t>20,9; 30,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,98; 37,09</t>
+          <t>27,11; 37,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,06; 33,15</t>
+          <t>23,94; 32,86</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,67</t>
+          <t>1,32; 8,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 15,37</t>
+          <t>5,51; 15,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 18,84</t>
+          <t>7,9; 19,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74,14; 93,05</t>
+          <t>73,8; 92,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,28; 80,72</t>
+          <t>57,07; 80,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,73; 73,58</t>
+          <t>52,31; 74,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,57; 33,08</t>
+          <t>20,36; 33,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,71; 35,87</t>
+          <t>23,19; 36,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,96; 37,1</t>
+          <t>24,71; 37,34</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,01; 19,65</t>
+          <t>9,18; 19,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 28,71</t>
+          <t>14,28; 29,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 23,49</t>
+          <t>12,23; 23,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,39; 90,73</t>
+          <t>73,02; 90,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,08; 85,89</t>
+          <t>69,88; 85,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,78; 78,6</t>
+          <t>60,84; 78,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,9; 42,24</t>
+          <t>30,63; 42,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 52,11</t>
+          <t>38,48; 52,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>34,9; 46,96</t>
+          <t>35,09; 46,58</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 21,08</t>
+          <t>5,54; 22,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 26,13</t>
+          <t>9,34; 26,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,74; 33,52</t>
+          <t>16,12; 33,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70,65; 93,25</t>
+          <t>67,67; 93,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,61; 78,44</t>
+          <t>54,78; 78,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,32; 72,26</t>
+          <t>49,33; 71,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,27; 47,74</t>
+          <t>30,95; 48,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,55; 47,54</t>
+          <t>30,74; 47,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,04; 48,52</t>
+          <t>32,4; 46,94</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,49</t>
+          <t>0,72; 7,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,24; 16,48</t>
+          <t>5,08; 15,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,91</t>
+          <t>1,06; 10,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>71,73; 90,46</t>
+          <t>72,4; 91,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,87; 68,61</t>
+          <t>47,24; 68,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,64; 81,64</t>
+          <t>58,35; 81,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,63; 34,75</t>
+          <t>22,15; 34,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,17; 36,77</t>
+          <t>24,24; 36,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,17; 40,37</t>
+          <t>25,89; 40,94</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 12,56</t>
+          <t>5,27; 12,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,18; 17,91</t>
+          <t>9,14; 17,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 14,4</t>
+          <t>6,08; 14,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72,42; 87,31</t>
+          <t>73,14; 87,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,33; 73,33</t>
+          <t>59,72; 73,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,56; 75,87</t>
+          <t>59,41; 76,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,2; 35,7</t>
+          <t>26,56; 35,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,16; 39,83</t>
+          <t>30,2; 40,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,4; 36,86</t>
+          <t>26,44; 36,73</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,76; 12,51</t>
+          <t>5,66; 11,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 12,51</t>
+          <t>6,2; 12,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,24; 19,56</t>
+          <t>11,48; 19,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74,77; 88,94</t>
+          <t>76,16; 89,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>60,58; 74,15</t>
+          <t>61,02; 74,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>63,9; 77,67</t>
+          <t>64,55; 78,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,62; 35,14</t>
+          <t>26,53; 35,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>27,67; 36,14</t>
+          <t>28,29; 36,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,6; 41,44</t>
+          <t>32,93; 41,62</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,08</t>
+          <t>6,17; 9,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,6</t>
+          <t>10,81; 14,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,32</t>
+          <t>10,83; 14,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79,79; 85,74</t>
+          <t>79,66; 85,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64,75; 70,87</t>
+          <t>64,87; 71,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,64; 69,35</t>
+          <t>62,96; 69,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,34; 32,26</t>
+          <t>28,29; 32,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32,72; 36,83</t>
+          <t>32,85; 36,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31,87; 36,1</t>
+          <t>31,98; 35,98</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4529; 15608</t>
+          <t>4471; 15126</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16484; 35938</t>
+          <t>15932; 35150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11085; 26385</t>
+          <t>10288; 26500</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29161; 35157</t>
+          <t>28166; 35142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37388; 53928</t>
+          <t>37766; 53571</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22784; 40533</t>
+          <t>23962; 41090</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31195; 51745</t>
+          <t>31878; 52852</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58305; 84709</t>
+          <t>58185; 84931</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38631; 62648</t>
+          <t>38704; 62641</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6198; 21414</t>
+          <t>6402; 21431</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11030; 29202</t>
+          <t>11492; 29872</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9015; 24963</t>
+          <t>8765; 25441</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62412; 77682</t>
+          <t>62815; 79135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87913; 110781</t>
+          <t>87764; 110172</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>90145; 113921</t>
+          <t>89735; 113578</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68690; 100508</t>
+          <t>68838; 99512</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>99676; 137019</t>
+          <t>100156; 137822</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99842; 137593</t>
+          <t>99367; 136406</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1872; 11167</t>
+          <t>1924; 11750</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8033; 21457</t>
+          <t>7699; 21164</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10851; 26138</t>
+          <t>10955; 27538</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42366; 53171</t>
+          <t>42173; 53136</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39192; 55233</t>
+          <t>39049; 54796</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38979; 56530</t>
+          <t>40193; 57050</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41720; 67080</t>
+          <t>41294; 66924</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>47242; 74631</t>
+          <t>48247; 74921</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53804; 79983</t>
+          <t>53274; 80482</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13222; 28841</t>
+          <t>13473; 29185</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18220; 38035</t>
+          <t>18921; 38959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18271; 36805</t>
+          <t>19167; 37563</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51974; 63385</t>
+          <t>51015; 63396</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65493; 81438</t>
+          <t>66255; 81483</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75400; 97504</t>
+          <t>75477; 96972</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64775; 91507</t>
+          <t>66368; 92265</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>87575; 118426</t>
+          <t>87450; 119040</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98001; 131859</t>
+          <t>98511; 130769</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4368; 16114</t>
+          <t>4239; 16945</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6764; 21456</t>
+          <t>7667; 21779</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14523; 30936</t>
+          <t>14873; 30659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32502; 42903</t>
+          <t>31134; 42963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35055; 50352</t>
+          <t>35164; 50611</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35826; 51447</t>
+          <t>35124; 51208</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37074; 58467</t>
+          <t>37896; 59726</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44700; 69551</t>
+          <t>44977; 69414</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>54018; 79326</t>
+          <t>52977; 76743</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>994; 8759</t>
+          <t>977; 9890</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6170; 19422</t>
+          <t>5985; 18275</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1020; 9390</t>
+          <t>1005; 9930</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43096; 54352</t>
+          <t>43499; 55128</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41248; 60383</t>
+          <t>41574; 59854</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41316; 57528</t>
+          <t>41115; 57310</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42209; 67808</t>
+          <t>43226; 68119</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49751; 75702</t>
+          <t>49893; 75990</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>41575; 66686</t>
+          <t>42769; 67618</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14533; 33166</t>
+          <t>13928; 32574</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24181; 47185</t>
+          <t>24070; 47062</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14482; 32994</t>
+          <t>13926; 33306</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85294; 102824</t>
+          <t>86138; 103496</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>104989; 132002</t>
+          <t>107494; 132493</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>82030; 106285</t>
+          <t>83230; 106701</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>100052; 136330</t>
+          <t>101439; 136804</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>133733; 176628</t>
+          <t>133916; 177402</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>97496; 136116</t>
+          <t>97638; 135611</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18023; 39121</t>
+          <t>17689; 36725</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19554; 40743</t>
+          <t>20178; 42208</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32583; 56692</t>
+          <t>33295; 56711</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99991; 118944</t>
+          <t>101858; 119791</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>127835; 156484</t>
+          <t>128761; 156903</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>119344; 145046</t>
+          <t>120551; 146252</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>118821; 156852</t>
+          <t>118426; 156606</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>148488; 193922</t>
+          <t>151810; 197033</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>155404; 197533</t>
+          <t>156956; 198400</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>87757; 128470</t>
+          <t>87341; 128270</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>148641; 200744</t>
+          <t>148660; 199512</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145447; 194464</t>
+          <t>147024; 194003</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>488369; 524803</t>
+          <t>487602; 524709</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>594825; 651059</t>
+          <t>595942; 654384</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>561515; 621681</t>
+          <t>564336; 621389</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>574679; 654034</t>
+          <t>573623; 658317</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>750687; 845000</t>
+          <t>753662; 847521</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>718371; 813686</t>
+          <t>720959; 811145</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P74B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,61; 15,61</t>
+          <t>3,81; 15,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,62; 38,87</t>
+          <t>17,78; 40,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 26,22</t>
+          <t>10,58; 26,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,21; 97,58</t>
+          <t>79,19; 97,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>56,65; 80,36</t>
+          <t>54,17; 79,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,66; 61,14</t>
+          <t>35,36; 59,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,98; 39,76</t>
+          <t>23,24; 39,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,04; 54,07</t>
+          <t>37,63; 54,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,0; 37,23</t>
+          <t>21,68; 37,11</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,01</t>
+          <t>2,59; 8,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 13,34</t>
+          <t>4,92; 13,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,97</t>
+          <t>3,35; 9,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68,68; 86,53</t>
+          <t>69,63; 85,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>60,3; 75,69</t>
+          <t>60,31; 75,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,16; 71,08</t>
+          <t>54,92; 72,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,9; 30,22</t>
+          <t>20,88; 30,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,11; 37,31</t>
+          <t>27,41; 37,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23,94; 32,86</t>
+          <t>24,19; 33,34</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 8,07</t>
+          <t>1,32; 8,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,51; 15,16</t>
+          <t>5,65; 15,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 19,85</t>
+          <t>7,81; 19,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73,8; 92,98</t>
+          <t>74,4; 93,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,07; 80,08</t>
+          <t>58,46; 80,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,31; 74,25</t>
+          <t>52,62; 74,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,36; 33,0</t>
+          <t>20,67; 33,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,19; 36,01</t>
+          <t>23,13; 36,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,71; 37,34</t>
+          <t>24,87; 37,39</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 19,88</t>
+          <t>9,11; 19,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,28; 29,41</t>
+          <t>13,6; 28,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,23; 23,97</t>
+          <t>12,0; 23,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73,02; 90,74</t>
+          <t>74,31; 90,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,88; 85,94</t>
+          <t>68,84; 86,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,84; 78,17</t>
+          <t>61,19; 78,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,63; 42,59</t>
+          <t>30,62; 43,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,48; 52,38</t>
+          <t>37,57; 51,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35,09; 46,58</t>
+          <t>35,04; 47,28</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 22,16</t>
+          <t>5,66; 21,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 26,52</t>
+          <t>8,14; 25,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,12; 33,22</t>
+          <t>16,22; 33,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,67; 93,38</t>
+          <t>70,21; 93,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,78; 78,85</t>
+          <t>54,16; 77,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,33; 71,92</t>
+          <t>49,35; 71,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,95; 48,77</t>
+          <t>30,47; 47,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,74; 47,44</t>
+          <t>29,95; 47,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32,4; 46,94</t>
+          <t>32,13; 46,8</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 7,32</t>
+          <t>0,73; 6,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,51</t>
+          <t>4,83; 15,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,48</t>
+          <t>1,1; 10,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72,4; 91,75</t>
+          <t>72,28; 91,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,24; 68,01</t>
+          <t>46,89; 68,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,35; 81,34</t>
+          <t>57,79; 81,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 34,91</t>
+          <t>21,93; 34,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,24; 36,91</t>
+          <t>23,65; 37,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,89; 40,94</t>
+          <t>25,58; 40,7</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,33</t>
+          <t>5,28; 12,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,14; 17,87</t>
+          <t>9,19; 18,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 14,53</t>
+          <t>6,2; 14,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>73,14; 87,88</t>
+          <t>72,65; 87,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,72; 73,61</t>
+          <t>59,56; 74,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,41; 76,17</t>
+          <t>58,77; 75,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,56; 35,82</t>
+          <t>26,41; 35,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,2; 40,01</t>
+          <t>30,46; 39,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,44; 36,73</t>
+          <t>27,03; 37,31</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 11,75</t>
+          <t>5,81; 12,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,2; 12,96</t>
+          <t>6,11; 12,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,48; 19,56</t>
+          <t>10,95; 19,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76,16; 89,57</t>
+          <t>76,31; 89,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,02; 74,35</t>
+          <t>60,8; 74,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,55; 78,31</t>
+          <t>64,22; 78,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,53; 35,08</t>
+          <t>27,01; 35,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>28,29; 36,72</t>
+          <t>28,31; 36,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,93; 41,62</t>
+          <t>32,72; 42,02</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,06</t>
+          <t>6,25; 9,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,51</t>
+          <t>10,75; 14,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,83; 14,29</t>
+          <t>10,76; 14,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>79,66; 85,73</t>
+          <t>79,55; 85,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64,87; 71,23</t>
+          <t>64,96; 71,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,96; 69,32</t>
+          <t>62,85; 69,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,29; 32,47</t>
+          <t>28,27; 32,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32,85; 36,94</t>
+          <t>32,8; 36,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31,98; 35,98</t>
+          <t>31,73; 35,65</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4471; 15126</t>
+          <t>3689; 14847</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15932; 35150</t>
+          <t>16076; 36233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10288; 26500</t>
+          <t>10690; 26805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28166; 35142</t>
+          <t>28517; 35159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>37766; 53571</t>
+          <t>36112; 53176</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23962; 41090</t>
+          <t>23761; 40311</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31878; 52852</t>
+          <t>30892; 51978</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>58185; 84931</t>
+          <t>59105; 86080</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38704; 62641</t>
+          <t>36484; 62451</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6402; 21431</t>
+          <t>6167; 20724</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11492; 29872</t>
+          <t>11010; 31224</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8765; 25441</t>
+          <t>8555; 24553</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62815; 79135</t>
+          <t>63683; 78420</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87764; 110172</t>
+          <t>87787; 109673</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89735; 113578</t>
+          <t>87755; 115278</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68838; 99512</t>
+          <t>68754; 99559</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100156; 137822</t>
+          <t>101252; 137827</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99367; 136406</t>
+          <t>100401; 138368</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1924; 11750</t>
+          <t>1929; 11972</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7699; 21164</t>
+          <t>7883; 20970</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10955; 27538</t>
+          <t>10829; 27101</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42173; 53136</t>
+          <t>42517; 53156</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>39049; 54796</t>
+          <t>40003; 55099</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40193; 57050</t>
+          <t>40427; 57100</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41294; 66924</t>
+          <t>41912; 67654</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>48247; 74921</t>
+          <t>48116; 74974</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>53274; 80482</t>
+          <t>53603; 80590</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13473; 29185</t>
+          <t>13379; 29284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18921; 38959</t>
+          <t>18016; 37703</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19167; 37563</t>
+          <t>18807; 37202</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51015; 63396</t>
+          <t>51913; 63383</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66255; 81483</t>
+          <t>65272; 81873</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75477; 96972</t>
+          <t>75913; 97348</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66368; 92265</t>
+          <t>66345; 93631</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>87450; 119040</t>
+          <t>85391; 117569</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>98511; 130769</t>
+          <t>98393; 132745</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4239; 16945</t>
+          <t>4326; 16384</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7667; 21779</t>
+          <t>6683; 20981</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14873; 30659</t>
+          <t>14969; 31274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31134; 42963</t>
+          <t>32300; 42951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>35164; 50611</t>
+          <t>34767; 49860</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35124; 51208</t>
+          <t>35136; 51025</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37896; 59726</t>
+          <t>37317; 58482</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>44977; 69414</t>
+          <t>43825; 69041</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52977; 76743</t>
+          <t>52526; 76513</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>977; 9890</t>
+          <t>982; 8885</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5985; 18275</t>
+          <t>5689; 17705</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1005; 9930</t>
+          <t>1039; 10135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43499; 55128</t>
+          <t>43430; 55037</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41574; 59854</t>
+          <t>41265; 60078</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41115; 57310</t>
+          <t>40719; 57536</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43226; 68119</t>
+          <t>42793; 67122</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49893; 75990</t>
+          <t>48690; 77180</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42769; 67618</t>
+          <t>42254; 67224</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13928; 32574</t>
+          <t>13951; 32067</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>24070; 47062</t>
+          <t>24208; 48175</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13926; 33306</t>
+          <t>14219; 34055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86138; 103496</t>
+          <t>85558; 103511</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>107494; 132493</t>
+          <t>107215; 133339</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>83230; 106701</t>
+          <t>82327; 105690</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>101439; 136804</t>
+          <t>100872; 136002</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>133916; 177402</t>
+          <t>135080; 176734</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>97638; 135611</t>
+          <t>99811; 137777</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17689; 36725</t>
+          <t>18174; 39686</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20178; 42208</t>
+          <t>19894; 41794</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33295; 56711</t>
+          <t>31736; 57252</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>101858; 119791</t>
+          <t>102056; 119344</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>128761; 156903</t>
+          <t>128303; 156262</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>120551; 146252</t>
+          <t>119940; 145701</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>118426; 156606</t>
+          <t>120576; 159525</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>151810; 197033</t>
+          <t>151924; 194121</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156956; 198400</t>
+          <t>155963; 200276</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>87341; 128270</t>
+          <t>88479; 128871</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>148660; 199512</t>
+          <t>147863; 200353</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>147024; 194003</t>
+          <t>146154; 195350</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>487602; 524709</t>
+          <t>486902; 525540</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>595942; 654384</t>
+          <t>596811; 652904</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>564336; 621389</t>
+          <t>563374; 623986</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>573623; 658317</t>
+          <t>573265; 654471</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>753662; 847521</t>
+          <t>752333; 845417</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>720959; 811145</t>
+          <t>715239; 803734</t>
         </is>
       </c>
     </row>
